--- a/app/data/data_evidence.xlsx
+++ b/app/data/data_evidence.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A04591C-6BDE-1846-B809-F220DC9B5522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49288BB1-CDD8-E54D-AF08-58779A0030AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="22580" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
+    <workbookView xWindow="-44340" yWindow="3460" windowWidth="36000" windowHeight="22580" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,15 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
   <si>
-    <t>Indikation</t>
-  </si>
-  <si>
-    <t>Evidenzlevel</t>
-  </si>
-  <si>
-    <t>Quelle</t>
-  </si>
-  <si>
     <t>Stand</t>
   </si>
   <si>
@@ -65,12 +56,6 @@
     <t>Lokalanästhetika</t>
   </si>
   <si>
-    <t>Halsschmerzen</t>
-  </si>
-  <si>
-    <t>Empfehlungsgrad</t>
-  </si>
-  <si>
     <t>systemische NSAID</t>
   </si>
   <si>
@@ -107,9 +92,6 @@
     <t>Hinweis</t>
   </si>
   <si>
-    <t>Cetylpyridiniumchlorid, Cetrimoniumbromid, Benzalkoniumchlorid, Dequaliniumchlorid, Amylmetacresol, 2,4.Dichlorbenzylalkohol</t>
-  </si>
-  <si>
     <t>Benzocain, Lidocain, Ambroxol</t>
   </si>
   <si>
@@ -119,9 +101,6 @@
     <t>Flurbiprofen, Benzydamin</t>
   </si>
   <si>
-    <t>Isländisch Moos, Hyaluronsäure, Carbomere</t>
-  </si>
-  <si>
     <t>Ia</t>
   </si>
   <si>
@@ -194,12 +173,6 @@
     <t>Xylometazolin, Oxymetazolin, Pseudoephedrin, Ephedrin</t>
   </si>
   <si>
-    <t>Wirkstoffgruppe</t>
-  </si>
-  <si>
-    <t>Wirkstoffe</t>
-  </si>
-  <si>
     <t>11/2025</t>
   </si>
   <si>
@@ -210,6 +183,33 @@
   </si>
   <si>
     <t>Dextromethorphan, Pentoxyverin, Levodropropizin</t>
+  </si>
+  <si>
+    <t>ind</t>
+  </si>
+  <si>
+    <t>ws_gruppe</t>
+  </si>
+  <si>
+    <t>drug</t>
+  </si>
+  <si>
+    <t>recom</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>evi</t>
+  </si>
+  <si>
+    <t>Cetylpyridiniumchlorid, Cetrimoniumbromid, Benzalkoniumchlorid, Dequaliniumchlorid, Amylmetacresol, 2,4-Dichlorbenzylalkohol</t>
+  </si>
+  <si>
+    <t>Halsschmerzen/Heiserkeit</t>
+  </si>
+  <si>
+    <t>Isländisches Moos, Hyaluronsäure, Carbomer</t>
   </si>
 </sst>
 </file>
@@ -607,415 +607,415 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>2</v>
-      </c>
-      <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">

--- a/app/data/data_evidence.xlsx
+++ b/app/data/data_evidence.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49288BB1-CDD8-E54D-AF08-58779A0030AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4470F8A1-4FDE-0A4E-B7A4-317A7867727B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-44340" yWindow="3460" windowWidth="36000" windowHeight="22580" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
+    <workbookView xWindow="-26100" yWindow="3460" windowWidth="19200" windowHeight="22440" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,15 +71,6 @@
     <t>Paracetamol</t>
   </si>
   <si>
-    <t>Ibuprofen, Naproxen</t>
-  </si>
-  <si>
-    <t>S2k-Leitlinie Rhinosinusitis (Stand 04/2017)</t>
-  </si>
-  <si>
-    <t>S3-Leitlinie Halsschmerzen (Stand 10/2020)</t>
-  </si>
-  <si>
     <t>Lokalantiseptika</t>
   </si>
   <si>
@@ -92,15 +83,9 @@
     <t>Hinweis</t>
   </si>
   <si>
-    <t>Benzocain, Lidocain, Ambroxol</t>
-  </si>
-  <si>
     <t>Tyrothricin</t>
   </si>
   <si>
-    <t>Flurbiprofen, Benzydamin</t>
-  </si>
-  <si>
     <t>Ia</t>
   </si>
   <si>
@@ -119,9 +104,6 @@
     <t>Antitussiva wirken hinsichtlich des Hustenreizes nicht besser als Placebo; können bei starkem nächtlichen Reizhusten auf ausdrücklichen Wunsch kurzzeitig eingesetzt werden</t>
   </si>
   <si>
-    <t>Ambroxol, Bromhexin, Acetylcystein</t>
-  </si>
-  <si>
     <t>synthetische Expektorantien</t>
   </si>
   <si>
@@ -131,9 +113,6 @@
     <t>keine-gering</t>
   </si>
   <si>
-    <t>S3-Leitlinie Akuter und chronischer Husten (Stand 11/2025)</t>
-  </si>
-  <si>
     <t>Phytotherapeutika</t>
   </si>
   <si>
@@ -143,36 +122,21 @@
     <t>können empfohlen werden</t>
   </si>
   <si>
-    <t>BNO 1016 (Sinupret extrakt), Cineol</t>
-  </si>
-  <si>
     <t>Kochsalzlösungen</t>
   </si>
   <si>
-    <t>Acetylsalicylsäure, Ibuprofen, Paracetamol</t>
-  </si>
-  <si>
     <t>Analgetika, NSAID</t>
   </si>
   <si>
     <t>zur symptomatischen Therapie; Acetylsalicylsäure, Ibuprofen &gt;&gt; Paracetamol</t>
   </si>
   <si>
-    <t>Efeu, Thymian, Primel, Myrtol, Cineol, Kombination ätherischer Öle, Eukalpytus</t>
-  </si>
-  <si>
-    <t>Salz, Meerwasser</t>
-  </si>
-  <si>
     <t>wirksam für kurzfristige Linderung von Nasenatmungsbehinderung; topische Dekongestiva ohne Benzalkoniumchlorid</t>
   </si>
   <si>
     <t>alpha-Sympathomimetika</t>
   </si>
   <si>
-    <t>Xylometazolin, Oxymetazolin, Pseudoephedrin, Ephedrin</t>
-  </si>
-  <si>
     <t>11/2025</t>
   </si>
   <si>
@@ -182,9 +146,6 @@
     <t>04/2017</t>
   </si>
   <si>
-    <t>Dextromethorphan, Pentoxyverin, Levodropropizin</t>
-  </si>
-  <si>
     <t>ind</t>
   </si>
   <si>
@@ -203,13 +164,52 @@
     <t>evi</t>
   </si>
   <si>
-    <t>Cetylpyridiniumchlorid, Cetrimoniumbromid, Benzalkoniumchlorid, Dequaliniumchlorid, Amylmetacresol, 2,4-Dichlorbenzylalkohol</t>
-  </si>
-  <si>
     <t>Halsschmerzen/Heiserkeit</t>
   </si>
   <si>
-    <t>Isländisches Moos, Hyaluronsäure, Carbomer</t>
+    <t>Dextromethorphan; Pentoxyverin; Levodropropizin</t>
+  </si>
+  <si>
+    <t>Ambroxol; Bromhexin; Acetylcystein</t>
+  </si>
+  <si>
+    <t>Efeu; Thymian; Primel; Myrtol; Cineol; Kombination ätherischer Öle; Eukalpytus</t>
+  </si>
+  <si>
+    <t>Isländisches Moos; Hyaluronsäure; Carbomer</t>
+  </si>
+  <si>
+    <t>Benzocain; Lidocain; Ambroxol</t>
+  </si>
+  <si>
+    <t>Flurbiprofen; Benzydamin</t>
+  </si>
+  <si>
+    <t>Ibuprofen; Naproxen</t>
+  </si>
+  <si>
+    <t>Xylometazolin; Oxymetazolin; Pseudoephedrin; Ephedrin</t>
+  </si>
+  <si>
+    <t>Acetylsalicylsäure; Ibuprofen; Paracetamol</t>
+  </si>
+  <si>
+    <t>BNO 1016 (Sinupret extrakt); Cineol</t>
+  </si>
+  <si>
+    <t>Salz; Meerwasser</t>
+  </si>
+  <si>
+    <t>Cetylpyridiniumchlorid; Cetrimoniumbromid; Benzalkoniumchlorid; Dequaliniumchlorid; Amylmetacresol; 2,4-Dichlorbenzylalkohol</t>
+  </si>
+  <si>
+    <t>S3-Leitlinie Akuter und chronischer Husten</t>
+  </si>
+  <si>
+    <t>S3-Leitlinie Halsschmerzen</t>
+  </si>
+  <si>
+    <t>S2k-Leitlinie Rhinosinusitis</t>
   </si>
 </sst>
 </file>
@@ -607,25 +607,25 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
         <v>0</v>
@@ -639,28 +639,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -668,26 +668,26 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -695,139 +695,139 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
@@ -836,74 +836,74 @@
         <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -911,28 +911,28 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -940,28 +940,28 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -969,26 +969,26 @@
         <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -996,26 +996,26 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">

--- a/app/data/data_evidence.xlsx
+++ b/app/data/data_evidence.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4470F8A1-4FDE-0A4E-B7A4-317A7867727B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F17D54F-FADA-BB47-A235-05135462DD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26100" yWindow="3460" windowWidth="19200" windowHeight="22440" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
+    <workbookView xWindow="4080" yWindow="2440" windowWidth="36140" windowHeight="23480" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -173,9 +173,6 @@
     <t>Ambroxol; Bromhexin; Acetylcystein</t>
   </si>
   <si>
-    <t>Efeu; Thymian; Primel; Myrtol; Cineol; Kombination ätherischer Öle; Eukalpytus</t>
-  </si>
-  <si>
     <t>Isländisches Moos; Hyaluronsäure; Carbomer</t>
   </si>
   <si>
@@ -210,6 +207,9 @@
   </si>
   <si>
     <t>S2k-Leitlinie Rhinosinusitis</t>
+  </si>
+  <si>
+    <t>Efeu; Thymian; Primel; Myrtol; Cineol; Eukalpytusöl; Myrtenöl; Kiefernnadelöl</t>
   </si>
 </sst>
 </file>
@@ -654,7 +654,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>33</v>
@@ -681,7 +681,7 @@
         <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>33</v>
@@ -698,7 +698,7 @@
         <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>27</v>
@@ -708,7 +708,7 @@
         <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>33</v>
@@ -725,7 +725,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>27</v>
@@ -735,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>34</v>
@@ -752,7 +752,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>27</v>
@@ -762,7 +762,7 @@
         <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>34</v>
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>27</v>
@@ -789,7 +789,7 @@
         <v>16</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>34</v>
@@ -806,7 +806,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>27</v>
@@ -816,7 +816,7 @@
         <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>34</v>
@@ -843,7 +843,7 @@
         <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>34</v>
@@ -860,7 +860,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
@@ -870,7 +870,7 @@
         <v>17</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>34</v>
@@ -897,7 +897,7 @@
         <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>34</v>
@@ -914,7 +914,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>27</v>
@@ -926,7 +926,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>35</v>
@@ -943,7 +943,7 @@
         <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>27</v>
@@ -955,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>35</v>
@@ -972,7 +972,7 @@
         <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>27</v>
@@ -982,7 +982,7 @@
         <v>23</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>35</v>
@@ -999,7 +999,7 @@
         <v>28</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>27</v>
@@ -1009,7 +1009,7 @@
         <v>23</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>35</v>

--- a/app/data/data_evidence.xlsx
+++ b/app/data/data_evidence.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanjana/Documents/01_projects/Pharmskills/pharmskills_app/app/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F17D54F-FADA-BB47-A235-05135462DD0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2605741-FAEE-F44E-91DE-932D1B1A386A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4080" yWindow="2440" windowWidth="36140" windowHeight="23480" xr2:uid="{67A7F374-70BF-0D43-951C-BB1EA0CD0AE7}"/>
   </bookViews>
